--- a/data/trans_orig/IP11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3856</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12288</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3529</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7369</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7791</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3829</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11997</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>114343</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>109092</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117524</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102642</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98802</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104965</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98380</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104885</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>114343</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>109383</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>117551</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211504</t>
+          <t>211506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221227</t>
+          <t>221250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10391</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13363</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8396</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19721</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8224</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19622</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10742</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23112</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38298</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>237696</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>230615</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>243365</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>239842</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>233484</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>244809</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>233583</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>244981</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>237696</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>230644</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>243014</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468663</t>
+          <t>468322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485452</t>
+          <t>485066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6433</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17060</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8794</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4869</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13741</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6317</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17600</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130455</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124455</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135082</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>118754</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>112693</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122679</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113807</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>122688</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130455</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>123915</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135198</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241077</t>
+          <t>240889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255452</t>
+          <t>255379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7551</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19148</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9618</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5644</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15544</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15480</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8042</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18651</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>193680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186901</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>198498</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>184479</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>178553</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>188453</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>178617</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>188552</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>193680</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>187398</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>198007</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369479</t>
+          <t>370201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>384801</t>
+          <t>384394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36682</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58494</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26187</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45694</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26221</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45310</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36605</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58829</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>96898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>676175</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>664206</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>686018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>645717</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>635327</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>654834</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>635711</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>654800</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>676175</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>663871</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>686095</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1981</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1307631</t>
+          <t>1306823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1334720</t>
+          <t>1333859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5699</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15435</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10712</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6319</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16387</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6547</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16663</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5208</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14779</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>134949</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>128724</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>138460</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135638</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129963</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>140031</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>129687</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>139803</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>134949</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129380</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>138951</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262798</t>
+          <t>263243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>276968</t>
+          <t>276728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144159</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144159</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144159</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146350</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146350</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146350</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144159</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144159</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20944</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37850</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18470</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12299</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26864</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12457</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26503</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>20267</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>37277</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>58019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>240753</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231141</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>248047</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>217780</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>209386</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>223951</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>209747</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>223793</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>240753</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>231714</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>248724</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447477</t>
+          <t>447222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>468465</t>
+          <t>468975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7288</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19774</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6424</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17608</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17210</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7127</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19721</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31713</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145506</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138190</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>150676</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>146266</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139435</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150619</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>139833</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150434</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>145506</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138243</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>150837</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283294</t>
+          <t>282279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298916</t>
+          <t>298464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157964</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157964</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157964</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157964</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157964</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16783</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31214</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11754</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7323</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18767</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7298</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18248</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16704</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45251</t>
+          <t>45559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156483</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148741</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163172</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>159583</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>152570</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164014</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153089</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>164039</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156483</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148588</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>163251</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>306041</t>
+          <t>305733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324191</t>
+          <t>324658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87643</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>40579</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>65077</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41292</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>63464</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>60540</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87567</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108681</t>
+          <t>108382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142229</t>
+          <t>143766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677692</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>663426</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>689933</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>659268</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645903</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>670401</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>647516</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>669688</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>677692</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>663502</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>690529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319820</t>
+          <t>1318283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1353368</t>
+          <t>1353667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4455</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6799</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123512</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130535</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128274</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>127199</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121425</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>117365</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>123429</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247563</t>
+          <t>247924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254429</t>
+          <t>254538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17983</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6346</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3012</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11760</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6868</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18266</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>246003</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>239399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>250220</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203270</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>198642</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206604</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197856</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206723</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,97%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>246003</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>239116</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250514</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440826</t>
+          <t>441964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454729</t>
+          <t>454805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257382</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257382</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257382</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209616</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257382</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257382</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257382</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7529</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18898</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6265</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3141</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11057</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11167</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7107</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18686</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>176381</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>169674</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>181043</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>182634</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177842</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>185758</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>177732</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>186145</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>176381</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>169886</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181465</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350411</t>
+          <t>351139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>364515</t>
+          <t>365163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20922</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9639</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15747</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5779</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16257</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8987</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20970</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158970</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152463</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164437</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162253</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156145</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>165921</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>155635</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166113</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>158970</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>152415</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>164398</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311816</t>
+          <t>312623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328365</t>
+          <t>328610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30622</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17224</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16176</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31456</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31377</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52052</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76910</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>702779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>691138</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>712881</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>678692</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670285</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>684837</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670605</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>685885</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702779</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>691451</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>712126</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1368654</t>
+          <t>1366773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1392867</t>
+          <t>1392908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49346</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56337</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54510</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>51165</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49718</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51731</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60107</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55937</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>220</t>
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116444</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113378</t>
+          <t>97675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117911</t>
+          <t>101716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9415</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7901</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152820</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>148107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>155581</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>155581</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151398</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157827</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>176996</t>
+          <t>141890</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>137698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180187</t>
+          <t>144110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>332577</t>
+          <t>294710</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325933</t>
+          <t>288149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336792</t>
+          <t>298753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14613</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1745</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10071</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15087</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>191605</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184514</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>195777</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>168194</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>163001</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>169750</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>165156</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>172756</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>203709</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>196324</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>207861</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>371902</t>
+          <t>361355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364912</t>
+          <t>352918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377027</t>
+          <t>366699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199127</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199127</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199127</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211411</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211411</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211411</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384483</t>
+          <t>373799</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384483</t>
+          <t>373799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384483</t>
+          <t>373799</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26775</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>267661</t>
+          <t>283809</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261932</t>
+          <t>277208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271831</t>
+          <t>288645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>296047</t>
+          <t>248484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288884</t>
+          <t>243329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300541</t>
+          <t>252662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>563707</t>
+          <t>532293</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554165</t>
+          <t>524096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569436</t>
+          <t>538365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14992</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10652</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25105</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52614</t>
+          <t>50648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667121</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684838</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>647773</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>639819</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>654272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>736858</t>
+          <t>611290</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725834</t>
+          <t>602830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744524</t>
+          <t>616610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1384631</t>
+          <t>1288870</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1373202</t>
+          <t>1277657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1395879</t>
+          <t>1298582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
